--- a/public/exports-60-250-with-coowners/29189757.xlsx
+++ b/public/exports-60-250-with-coowners/29189757.xlsx
@@ -6514,7 +6514,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257874</t>
+          <t xml:space="preserve">311257717</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
